--- a/data/RETENCOES_REGRAS.xlsx
+++ b/data/RETENCOES_REGRAS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikaellesantos\Desktop\VALIDADOR DE NOTAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaio.paula\Downloads\0153d67d-8cc4-4180-b01a-cd4efcd965bb\Backend_cl\Backend_Auditoria\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D90538-E386-4C71-B413-154E6F84DEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FBF957-7042-412D-A425-84BC715648FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{A235ED8A-DA4F-4847-AD66-F6377633532B}"/>
   </bookViews>
@@ -3881,7 +3881,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="F83" t="s">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="G83" t="s">
         <v>255</v>
